--- a/data/raw/inventory/Week 35/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 35/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -1279,7 +1279,7 @@
         <v>25</v>
       </c>
       <c r="F14" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>25</v>
@@ -1651,7 +1651,7 @@
         <v>229</v>
       </c>
       <c r="F20" t="n">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K20" t="n">
         <v>230</v>

--- a/data/raw/inventory/Week 35/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 35/White_Mulberry/Seller FBA Inventory (SP-API).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P52"/>
+  <dimension ref="A1:P51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2063,12 +2063,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>FBA76388</t>
+          <t>FBA76415</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>B0BF4VRJJ1</t>
+          <t>B0BFWD6SNF</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2078,35 +2078,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>WM-SEH04P-WH</t>
+          <t>WM-LOD-CF</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -2125,12 +2125,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>FBA76415</t>
+          <t>FBA76416</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>B0BFWD6SNF</t>
+          <t>B0BFW59TRG</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2140,35 +2140,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>WM-LOD-CF</t>
+          <t>WM-LOD-BK</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="F28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
       <c r="J28" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="L28" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -2187,12 +2187,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>FBA76416</t>
+          <t>FBA76417</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>B0BFW59TRG</t>
+          <t>B0BFVMDJ2K</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>WM-LOD-BK</t>
+          <t>WM-LOD-WH</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="F29" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="K29" t="n">
-        <v>24</v>
+        <v>95</v>
       </c>
       <c r="L29" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2249,12 +2249,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FBA76417</t>
+          <t>FBA76418</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>B0BFVMDJ2K</t>
+          <t>B0BFVNS8HS</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2264,32 +2264,32 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>WM-LOD-WH</t>
+          <t>WM-LOD-IN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="F30" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="K30" t="n">
-        <v>95</v>
+        <v>45</v>
       </c>
       <c r="L30" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -2311,12 +2311,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>FBA76418</t>
+          <t>FBA76765</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>B0BFVNS8HS</t>
+          <t>B0BMQQQ7YD</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2326,20 +2326,20 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>WM-LOD-IN</t>
+          <t>WM-SEH04P-CF</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="F31" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -2348,10 +2348,10 @@
         <v>1</v>
       </c>
       <c r="K31" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -2373,12 +2373,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>FBA76765</t>
+          <t>FBA79164</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>B0BMQQQ7YD</t>
+          <t>B0CPFN27Z2</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2388,11 +2388,11 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>WM-SEH04P-CF</t>
+          <t>WM-USE06-BK</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2407,13 +2407,13 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -2435,12 +2435,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>FBA79164</t>
+          <t>FBA79165</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>B0CPFN27Z2</t>
+          <t>B0CPFPT6DZ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2450,11 +2450,11 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>WM-USE06-BK</t>
+          <t>WM-USE06-WH</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -2469,13 +2469,13 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
         <v>0</v>
@@ -2497,12 +2497,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>FBA79165</t>
+          <t>FBA79167</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>B0CPFPT6DZ</t>
+          <t>B0CPFS24ML</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2512,32 +2512,32 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>WM-USE06-WH</t>
+          <t>WM-GD07-CB</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -2559,12 +2559,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>FBA79167</t>
+          <t>FBA79175</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>B0CPFS24ML</t>
+          <t>B0CPT2YJX2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2574,32 +2574,32 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>WM-GD07-CB</t>
+          <t>WM-SMD09-WH</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>203</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>207</v>
+        <v>1</v>
       </c>
       <c r="L35" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -2621,12 +2621,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>FBA79175</t>
+          <t>FBA79177</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>B0CPT2YJX2</t>
+          <t>B0CPT34B2L</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>WM-SMD09-WH</t>
+          <t>WM-SE08-BK</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -2683,12 +2683,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>FBA79177</t>
+          <t>FBA79178</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>B0CPT34B2L</t>
+          <t>B0CPT2NY5M</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2698,14 +2698,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>WM-SE08-BK</t>
+          <t>WM-SE08-WH</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2717,13 +2717,13 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -2745,12 +2745,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FBA79178</t>
+          <t>FBA79179</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>B0CPT2NY5M</t>
+          <t>B0CPT3Q25C</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2760,35 +2760,35 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>WM-SE08-WH</t>
+          <t>WM-SE08-CF</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="inlineStr">
         <is>
@@ -2807,12 +2807,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>FBA79179</t>
+          <t>FBA79433</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>B0CPT3Q25C</t>
+          <t>B0DC3JRBW1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2822,20 +2822,20 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>WM-SE08-CF</t>
+          <t>WM-SE08-WD</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -2844,13 +2844,13 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -2869,12 +2869,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FBA79433</t>
+          <t>FBA79479</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B0DC3JRBW1</t>
+          <t>B0DB5YTQZV</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>WM-SE08-WD</t>
+          <t>WM-HA2M-BK</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -2906,10 +2906,10 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -2931,12 +2931,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FBA79479</t>
+          <t>FBA79617</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>B0DB5YTQZV</t>
+          <t>B0DP32F346</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>WM-HA2M-BK</t>
+          <t>HDWF1ML</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -2968,7 +2968,7 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -2993,12 +2993,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FBA79617</t>
+          <t>FBA79658</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B0DP32F346</t>
+          <t>B0DQ1PKNSP</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -3008,14 +3008,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>HDWF1ML</t>
+          <t>WM-MDL-WH</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M42" t="n">
         <v>0</v>
@@ -3055,12 +3055,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FBA79658</t>
+          <t>FBA79659</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B0DQ1PKNSP</t>
+          <t>B0DQ1NV8D2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>WM-MDL-WH</t>
+          <t>WM-MDL-BK</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -3092,10 +3092,10 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -3117,12 +3117,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FBA79659</t>
+          <t>FBA79661</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>B0DQ1NV8D2</t>
+          <t>B0DQ51R95T</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3132,11 +3132,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>WM-MDL-BK</t>
+          <t>WM-MODL-BK</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F44" t="n">
         <v>0</v>
@@ -3151,13 +3151,13 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M44" t="n">
         <v>0</v>
@@ -3179,12 +3179,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FBA79661</t>
+          <t>FBA79662</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>B0DQ51R95T</t>
+          <t>B0DQ4YWSMC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3194,11 +3194,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>WM-MODL-BK</t>
+          <t>WM-MODL-WH</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -3207,16 +3207,16 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="L45" t="n">
         <v>2</v>
@@ -3241,12 +3241,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FBA79662</t>
+          <t>FBA79667</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>B0DQ4YWSMC</t>
+          <t>B0DQPK7MFH</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3256,11 +3256,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>WM-MODL-WH</t>
+          <t>WM-LODN-WH</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -3278,10 +3278,10 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -3303,12 +3303,12 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FBA79667</t>
+          <t>FBA79668</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>B0DQPK7MFH</t>
+          <t>B0CPT2YJX2</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>WM-LODN-WH</t>
+          <t>WM-SMD09-WH</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -3340,10 +3340,10 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
         <v>0</v>
@@ -3365,12 +3365,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FBA79668</t>
+          <t>FBA79669</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>B0CPT2YJX2</t>
+          <t>B0DQPLMQQ7</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>WM-SMD09-WH</t>
+          <t>WM-LWS-CF</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -3402,10 +3402,10 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -3427,12 +3427,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FBA79669</t>
+          <t>FBI76419</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>B0DQPLMQQ7</t>
+          <t>B07MH7L6G8</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>WM-LWS-CF</t>
+          <t>WM-OD-CL</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -3489,12 +3489,12 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FBI76419</t>
+          <t>FBK76387</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B07MH7L6G8</t>
+          <t>B0BF4S7V8C</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3504,7 +3504,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>WM-OD-CL</t>
+          <t>WM-MH05P-WH</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -3526,10 +3526,10 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>0</v>
@@ -3551,12 +3551,12 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>FBK76387</t>
+          <t>FBK76764</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B0BF4S7V8C</t>
+          <t>B0BMV1WPHL</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>WM-MH05P-WH</t>
+          <t>WM-MH05P-CF</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -3588,10 +3588,10 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -3607,68 +3607,6 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>FBK76764</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>B0BMV1WPHL</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>White Mulberry</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>WM-MH05P-CF</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="n">
-        <v>1</v>
-      </c>
-      <c r="L52" t="n">
-        <v>1</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>WHITEMULBERRY</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>2026-08-29</t>
-        </is>
-      </c>
-      <c r="P52" t="n">
         <v>35</v>
       </c>
     </row>
